--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -512,41 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.5</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>17924</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.58333333334</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15220</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45522.5</v>
+        <v>45521.66666666666</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.41666666666</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>17924</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,7 +827,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -836,32 +836,32 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,7 +890,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -899,32 +899,32 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,7 +953,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -962,32 +962,32 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29778</v>
+        <v>33150</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1016,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45522.5</v>
+        <v>45522.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>29778</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,419 +512,419 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45522.5</v>
+        <v>45520.65625</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45521.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45521.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45521.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Stade Raymond-Kopa
  (Angers)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E7" t="n">
         <v>18752</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>SAlF91iL</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Angers</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>551</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>45522.5</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Stade de la Mosson
  (Montpellier)</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>20484</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,7 +953,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -962,115 +962,682 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Roazhon Park
  (Rennes)</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>29778</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45522.5</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>33150</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>MLmY2yB1</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Toulouse</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,573 +1071,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,510 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45527.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>38223</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Angoula G.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>35322</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.66666666666</v>
+        <v>45529.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Batta F.
+          <t>Dechepy B.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -708,6 +708,709 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45529.65625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pignard J.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45534.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38223</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +575,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45535.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35322</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36178</v>
+        <v>20484</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26109</v>
+        <v>33150</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67394</v>
+        <v>18523</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,41 +827,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>59186</v>
+        <v>18752</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -915,41 +890,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>25178</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -978,41 +953,41 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>21029</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1041,41 +1016,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>50186</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1096,321 +1071,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,41 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.65625</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>45535.5</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>59186</v>
+        <v>15220</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -575,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,41 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.58333333334</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>45535.66666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20484</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -701,41 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.66666666666</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>45536.41666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -764,41 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>45536.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -827,41 +852,46 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -890,41 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25178</v>
+        <v>21029</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -953,41 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>45536.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21029</v>
+        <v>50186</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1008,69 +1048,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Millot B.
+          <t>Stinat J.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>20484</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.66666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.41666666666</v>
+        <v>45536.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18523</v>
+        <v>21029</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18752</v>
+        <v>50186</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,210 +844,6 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Vernice M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>551</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,41 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45548.65625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>42000</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,36 +575,31 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Stinat J.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45549.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>67394</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -648,46 +638,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45549.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25178</v>
+        <v>17924</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +701,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Vernice M.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Parc des Princes
+ (Paris)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>48229</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +764,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -844,6 +819,258 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,573 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,338 +512,1172 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45556.5</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>551</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
  (Nantes)</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E18" t="n">
         <v>35322</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E19" t="n">
         <v>26109</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45555.65625</v>
+        <v>45556.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Leonard T.
+          <t>Brisard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36178</v>
+        <v>50186</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,41 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.5</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>45556.58333333334</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>29778</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -643,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.58333333334</v>
+        <v>45556.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29778</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -711,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.66666666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pignard J.
+          <t>Frappart S.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21029</v>
+        <v>18523</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -779,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45557.41666666666</v>
+        <v>45557.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>18523</v>
+        <v>18752</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -847,7 +852,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -855,38 +860,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Batta F.
  (Fra)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18752</v>
+        <v>15220</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -915,7 +920,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -923,38 +928,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Batta F.
+          <t>Ben El Hadj Salem H.
  (Fra)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15220</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -983,46 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45557.5</v>
+        <v>45557.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ben El Hadj Salem H.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20484</v>
+        <v>59186</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1043,641 +1048,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45557.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45562.58333333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45562.66666666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.58333333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,338 +512,1132 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pignard J.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45562.58333333334</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.5</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.58333333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25178</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.5</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Roazhon Park
  (Rennes)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E14" t="n">
         <v>29778</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>551</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E18" t="n">
         <v>26109</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45550.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,12 @@
       <c r="B2" s="2" t="n">
         <v>45562.58333333334</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stade de l'Abbé-Deschamps
@@ -581,7 +586,12 @@
       <c r="B3" s="2" t="n">
         <v>45562.66666666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Parc des Princes
@@ -644,7 +654,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.5</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Stade Bollaert-Delelis
@@ -707,7 +722,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.58333333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Stade Océane
@@ -770,7 +790,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.66666666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Stade Louis II
@@ -833,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stadium Municipal
@@ -896,7 +926,12 @@
       <c r="B8" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Stade Raymond-Kopa
@@ -959,7 +994,12 @@
       <c r="B9" s="2" t="n">
         <v>45564.5</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
@@ -1022,7 +1062,12 @@
       <c r="B10" s="2" t="n">
         <v>45564.65625</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Stade de la Meinau
@@ -1071,573 +1116,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.65625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.58333333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.66666666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>21029</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.58333333334</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Angoula G.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17924</v>
+        <v>33150</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben El Hadj Salem H.
+          <t>Wattellier E.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Parc des Princes
- (Paris)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48229</v>
+        <v>18752</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.5</v>
+        <v>45564.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Letexier F.
+          <t>Kherradji A.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38223</v>
+        <v>35322</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.58333333334</v>
+        <v>45564.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dechepy B.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25178</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -776,346 +776,6 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>551</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Kherradji A.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Lissorgue R.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33150</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wattellier E.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18752</v>
+        <v>42000</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5</v>
+        <v>45570.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Turpin C.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35322</v>
+        <v>50186</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,66 +716,469 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Leonard T.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E9" t="n">
         <v>26109</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>55</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L9" t="n">
         <v>551</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N9" t="n">
         <v>20242025</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lissorgue R.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67394</v>
+        <v>59186</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.5</v>
+        <v>45571.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Millot B.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>15220</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.58333333334</v>
+        <v>45571.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turpin C.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50186</v>
+        <v>21029</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45571.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leonard T.
+          <t>Frappart S.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29778</v>
+        <v>26109</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bollengier M.
+          <t>Brisard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>59186</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,46 +852,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Millot B.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45583.65625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15220</v>
+        <v>18523</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -920,46 +915,41 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45584.5</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21029</v>
+        <v>15220</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -988,36 +978,31 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.5</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Frappart S.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45584.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26109</v>
+        <v>42000</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1056,46 +1041,41 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brisard J.
- (Fra)</t>
-        </is>
-      </c>
+        <v>45584.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Parc des Princes
+ (Paris)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36178</v>
+        <v>48229</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1124,41 +1104,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.65625</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18523</v>
+        <v>25178</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1179,6 +1159,258 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>35322</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,338 +512,1172 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Batta F.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>29778</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>18752</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.58333333334</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21029</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>59186</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20484</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>36178</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26109</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>67394</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>50186</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>15220</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>17924</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade Océane
  (Le Havre)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E18" t="n">
         <v>25178</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>CIEe04GT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>551</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Batta F.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
  (Nantes)</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E19" t="n">
         <v>35322</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45585.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Turpin C.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>SblU3Hee</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Marseille</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,7 +858,12 @@
       <c r="B7" s="2" t="n">
         <v>45592.54166666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stade de la Mosson
@@ -1111,573 +1116,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45597.625</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>18523</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>50186</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.54166666666</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>48229</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>15220</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42000</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>33150</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>17924</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>35322</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,573 +1116,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45604.69791666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>67394</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.54166666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>26109</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.625</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>38223</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>18752</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>36178</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>25178</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>20484</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.54166666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>29778</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.69791666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>59186</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -512,46 +512,46 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.625</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>18523</v>
+        <v>67394</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -580,46 +580,46 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45605.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brisard J.
+          <t>Dechepy B.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50186</v>
+        <v>26109</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,46 +648,46 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.54166666666</v>
+        <v>45605.625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Turpin C.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Parc des Princes
- (Paris)</t>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48229</v>
+        <v>38223</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -716,46 +716,46 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turpin C.
+          <t>Millot B.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15220</v>
+        <v>18752</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,46 +784,46 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.70833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wattellier E.
+          <t>Stinat J.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42000</v>
+        <v>36178</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -852,36 +852,36 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Ben El Hadj Salem H.
  (Fra)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33150</v>
+        <v>25178</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -920,46 +920,46 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17924</v>
+        <v>20484</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -988,46 +988,46 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45606.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Lissorgue R.
  (Fra)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25178</v>
+        <v>29778</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1056,46 +1056,46 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dechepy B.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35322</v>
+        <v>59186</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
+++ b/data/france/p6_deployment/data_preparation/format_data/df_match_form.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,258 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>18523</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45618.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>48229</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.54166666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38223</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.625</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
